--- a/erp-server/erp-server-plm/src/main/resources/excel/productWarehouseLocationError.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productWarehouseLocationError.xlsx
@@ -4,19 +4,39 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="23130" windowHeight="11850"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -30,18 +50,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>仓位编号</t>
-    </r>
+    <t>推荐仓位(小货区)</t>
+  </si>
+  <si>
+    <t>推荐仓位(大货区)</t>
   </si>
   <si>
     <t>错误信息</t>
@@ -53,13 +65,16 @@
     <t>{.warehouseLocation}</t>
   </si>
   <si>
+    <t>{.warehouseLocationLarge}</t>
+  </si>
+  <si>
     <t>{.errorMsg}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -89,6 +104,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -230,12 +251,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -574,137 +589,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -712,7 +727,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1065,33 +1083,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="2"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="2" width="14.4583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.25" customWidth="1"/>
+    <col min="1" max="1" width="14.4583333333333" customWidth="1"/>
+    <col min="2" max="3" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="22.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:3">
+    <row r="1" s="1" customFormat="1" ht="12" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
